--- a/site/Dayforce-to-Active-Directory-and-Entra-ID-Integration-Guide/headings.xlsx
+++ b/site/Dayforce-to-Active-Directory-and-Entra-ID-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -627,12 +627,144 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>h_01KMMBSG1HKCWYHM8EKS17PQY3</t>
+          <t>h_01KMQ7T44VZFB5PBARG0TYREKF</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-Active-Directory-and-Entra-ID-Integration-Guide/#h_01KMMBSG1HKCWYHM8EKS17PQY3</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-Active-Directory-and-Entra-ID-Integration-Guide/#h_01KMQ7T44VZFB5PBARG0TYREKF</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Directory</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>h_01KMQ7TNEHPPD4BK4XJK83E7J3</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-Active-Directory-and-Entra-ID-Integration-Guide/#h_01KMQ7TNEHPPD4BK4XJK83E7J3</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Policy</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>h_01KMQ7TX7BWSQ5G56YKZ7PKWND</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-Active-Directory-and-Entra-ID-Integration-Guide/#h_01KMQ7TX7BWSQ5G56YKZ7PKWND</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Execution</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>h_01KMQ7V436R8NAB6DY1Q9CZ0K6</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-Active-Directory-and-Entra-ID-Integration-Guide/#h_01KMQ7V436R8NAB6DY1Q9CZ0K6</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Notification Center</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>h_01KMQ7VBW5CRXEP8KGFHBYG161</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-Active-Directory-and-Entra-ID-Integration-Guide/#h_01KMQ7VBW5CRXEP8KGFHBYG161</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Tables</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>h_01KMQ7WN0WEE2127MZ5RDTFBWD</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-Active-Directory-and-Entra-ID-Integration-Guide/#h_01KMQ7WN0WEE2127MZ5RDTFBWD</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Schedule</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>h_01KMQ7VRVT1E4AD0BFY20V8496</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-Active-Directory-and-Entra-ID-Integration-Guide/#h_01KMQ7VRVT1E4AD0BFY20V8496</t>
         </is>
       </c>
     </row>

--- a/site/Dayforce-to-Active-Directory-and-Entra-ID-Integration-Guide/headings.xlsx
+++ b/site/Dayforce-to-Active-Directory-and-Entra-ID-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:D18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -617,7 +617,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Application Settings</t>
+          <t>Application Settings / Source Configuration</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -639,51 +639,51 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Directory</t>
+          <t>Identity Source Configuration / Source Configuration for Employee Management</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>h_01KMQ7TNEHPPD4BK4XJK83E7J3</t>
+          <t>h_01KMQ8T0H858Q6EASJRRVCJA22</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-Active-Directory-and-Entra-ID-Integration-Guide/#h_01KMQ7TNEHPPD4BK4XJK83E7J3</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-Active-Directory-and-Entra-ID-Integration-Guide/#h_01KMQ8T0H858Q6EASJRRVCJA22</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Policy</t>
+          <t>Candidate Source Configuration / Source Configuration for Candidate Management</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>h_01KMQ7TX7BWSQ5G56YKZ7PKWND</t>
+          <t>h_01KMQCT0XY99W85BRVSR9VG555</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-Active-Directory-and-Entra-ID-Integration-Guide/#h_01KMQ7TX7BWSQ5G56YKZ7PKWND</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-Active-Directory-and-Entra-ID-Integration-Guide/#h_01KMQCT0XY99W85BRVSR9VG555</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Execution</t>
+          <t>Directory</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -693,19 +693,19 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>h_01KMQ7V436R8NAB6DY1Q9CZ0K6</t>
+          <t>h_01KMQ95W0VKEWZT0G3MVJZ0SR8</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-Active-Directory-and-Entra-ID-Integration-Guide/#h_01KMQ7V436R8NAB6DY1Q9CZ0K6</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-Active-Directory-and-Entra-ID-Integration-Guide/#h_01KMQ95W0VKEWZT0G3MVJZ0SR8</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Notification Center</t>
+          <t>Policy</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -715,19 +715,19 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>h_01KMQ7VBW5CRXEP8KGFHBYG161</t>
+          <t>h_01KMQ7TX7BWSQ5G56YKZ7PKWND</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-Active-Directory-and-Entra-ID-Integration-Guide/#h_01KMQ7VBW5CRXEP8KGFHBYG161</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-Active-Directory-and-Entra-ID-Integration-Guide/#h_01KMQ7TX7BWSQ5G56YKZ7PKWND</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Tables</t>
+          <t>Execution</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -737,32 +737,76 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>h_01KMQ7WN0WEE2127MZ5RDTFBWD</t>
+          <t>h_01KMQ7V436R8NAB6DY1Q9CZ0K6</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-Active-Directory-and-Entra-ID-Integration-Guide/#h_01KMQ7WN0WEE2127MZ5RDTFBWD</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-Active-Directory-and-Entra-ID-Integration-Guide/#h_01KMQ7V436R8NAB6DY1Q9CZ0K6</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>Notification Center</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>h_01KMQ7VBW5CRXEP8KGFHBYG161</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-Active-Directory-and-Entra-ID-Integration-Guide/#h_01KMQ7VBW5CRXEP8KGFHBYG161</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Tables</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>h_01KMQ7WN0WEE2127MZ5RDTFBWD</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-Active-Directory-and-Entra-ID-Integration-Guide/#h_01KMQ7WN0WEE2127MZ5RDTFBWD</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>Schedule</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>H2</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
         <is>
           <t>h_01KMQ7VRVT1E4AD0BFY20V8496</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-Active-Directory-and-Entra-ID-Integration-Guide/#h_01KMQ7VRVT1E4AD0BFY20V8496</t>
         </is>

--- a/site/Dayforce-to-Active-Directory-and-Entra-ID-Integration-Guide/headings.xlsx
+++ b/site/Dayforce-to-Active-Directory-and-Entra-ID-Integration-Guide/headings.xlsx
@@ -671,12 +671,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>h_01KMQCT0XY99W85BRVSR9VG555</t>
+          <t>h_01KMQEVHA1EDRHNJGMT9QAZBD4</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-Active-Directory-and-Entra-ID-Integration-Guide/#h_01KMQCT0XY99W85BRVSR9VG555</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-Active-Directory-and-Entra-ID-Integration-Guide/#h_01KMQEVHA1EDRHNJGMT9QAZBD4</t>
         </is>
       </c>
     </row>

--- a/site/Dayforce-to-Active-Directory-and-Entra-ID-Integration-Guide/headings.xlsx
+++ b/site/Dayforce-to-Active-Directory-and-Entra-ID-Integration-Guide/headings.xlsx
@@ -671,12 +671,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>h_01KMQEVHA1EDRHNJGMT9QAZBD4</t>
+          <t>h_01KMQNGJCFQZN9JT6F2P6Z0TBM</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-Active-Directory-and-Entra-ID-Integration-Guide/#h_01KMQEVHA1EDRHNJGMT9QAZBD4</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-Active-Directory-and-Entra-ID-Integration-Guide/#h_01KMQNGJCFQZN9JT6F2P6Z0TBM</t>
         </is>
       </c>
     </row>

--- a/site/Dayforce-to-Active-Directory-and-Entra-ID-Integration-Guide/headings.xlsx
+++ b/site/Dayforce-to-Active-Directory-and-Entra-ID-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D18"/>
+  <dimension ref="A1:D19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -683,29 +683,29 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Directory</t>
+          <t>Time Based Settings / Time Zone Configuration</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>h_01KMQ95W0VKEWZT0G3MVJZ0SR8</t>
+          <t>h_01KMZCBQ6HVBJ5DXGJ4971WR1H</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-Active-Directory-and-Entra-ID-Integration-Guide/#h_01KMQ95W0VKEWZT0G3MVJZ0SR8</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-Active-Directory-and-Entra-ID-Integration-Guide/#h_01KMZCBQ6HVBJ5DXGJ4971WR1H</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Policy</t>
+          <t>Directory</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -715,19 +715,19 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>h_01KMQ7TX7BWSQ5G56YKZ7PKWND</t>
+          <t>h_01KMQ95W0VKEWZT0G3MVJZ0SR8</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-Active-Directory-and-Entra-ID-Integration-Guide/#h_01KMQ7TX7BWSQ5G56YKZ7PKWND</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-Active-Directory-and-Entra-ID-Integration-Guide/#h_01KMQ95W0VKEWZT0G3MVJZ0SR8</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Execution</t>
+          <t>Policy</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -737,19 +737,19 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>h_01KMQ7V436R8NAB6DY1Q9CZ0K6</t>
+          <t>h_01KMQ7TX7BWSQ5G56YKZ7PKWND</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-Active-Directory-and-Entra-ID-Integration-Guide/#h_01KMQ7V436R8NAB6DY1Q9CZ0K6</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-Active-Directory-and-Entra-ID-Integration-Guide/#h_01KMQ7TX7BWSQ5G56YKZ7PKWND</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Notification Center</t>
+          <t>Execution</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -759,19 +759,19 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>h_01KMQ7VBW5CRXEP8KGFHBYG161</t>
+          <t>h_01KMQ7V436R8NAB6DY1Q9CZ0K6</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-Active-Directory-and-Entra-ID-Integration-Guide/#h_01KMQ7VBW5CRXEP8KGFHBYG161</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-Active-Directory-and-Entra-ID-Integration-Guide/#h_01KMQ7V436R8NAB6DY1Q9CZ0K6</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Tables</t>
+          <t>Notification Center</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -781,32 +781,54 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>h_01KMQ7WN0WEE2127MZ5RDTFBWD</t>
+          <t>h_01KMQ7VBW5CRXEP8KGFHBYG161</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-Active-Directory-and-Entra-ID-Integration-Guide/#h_01KMQ7WN0WEE2127MZ5RDTFBWD</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-Active-Directory-and-Entra-ID-Integration-Guide/#h_01KMQ7VBW5CRXEP8KGFHBYG161</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>Tables</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>h_01KMQ7WN0WEE2127MZ5RDTFBWD</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-Active-Directory-and-Entra-ID-Integration-Guide/#h_01KMQ7WN0WEE2127MZ5RDTFBWD</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>Schedule</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>H2</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
         <is>
           <t>h_01KMQ7VRVT1E4AD0BFY20V8496</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-Active-Directory-and-Entra-ID-Integration-Guide/#h_01KMQ7VRVT1E4AD0BFY20V8496</t>
         </is>

--- a/site/Dayforce-to-Active-Directory-and-Entra-ID-Integration-Guide/headings.xlsx
+++ b/site/Dayforce-to-Active-Directory-and-Entra-ID-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -683,7 +683,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Time Based Settings / Time Zone Configuration</t>
+          <t>Time Based Settings / Timezone Configuration</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -693,63 +693,63 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>h_01KMZCBQ6HVBJ5DXGJ4971WR1H</t>
+          <t>h_01KMZHBBGFSRX4RBMD3WW86DCN</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-Active-Directory-and-Entra-ID-Integration-Guide/#h_01KMZCBQ6HVBJ5DXGJ4971WR1H</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-Active-Directory-and-Entra-ID-Integration-Guide/#h_01KMZHBBGFSRX4RBMD3WW86DCN</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Directory</t>
+          <t>Attribute Cache / Can be moved to Source Configuration section?</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>h_01KMQ95W0VKEWZT0G3MVJZ0SR8</t>
+          <t>h_01KMZHBBGG0RGHQ04VVAP3J6RJ</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-Active-Directory-and-Entra-ID-Integration-Guide/#h_01KMQ95W0VKEWZT0G3MVJZ0SR8</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-Active-Directory-and-Entra-ID-Integration-Guide/#h_01KMZHBBGG0RGHQ04VVAP3J6RJ</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Policy</t>
+          <t>PII Attributes / Can be moved under policy</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>h_01KMQ7TX7BWSQ5G56YKZ7PKWND</t>
+          <t>h_01KMZHBBGG9D8BERBETDSS9G8J</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-Active-Directory-and-Entra-ID-Integration-Guide/#h_01KMQ7TX7BWSQ5G56YKZ7PKWND</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-Active-Directory-and-Entra-ID-Integration-Guide/#h_01KMZHBBGG9D8BERBETDSS9G8J</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Execution</t>
+          <t>Directory</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -759,41 +759,41 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>h_01KMQ7V436R8NAB6DY1Q9CZ0K6</t>
+          <t>h_01KMQ95W0VKEWZT0G3MVJZ0SR8</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-Active-Directory-and-Entra-ID-Integration-Guide/#h_01KMQ7V436R8NAB6DY1Q9CZ0K6</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-Active-Directory-and-Entra-ID-Integration-Guide/#h_01KMQ95W0VKEWZT0G3MVJZ0SR8</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Notification Center</t>
+          <t>Mailbox Settings</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>h_01KMQ7VBW5CRXEP8KGFHBYG161</t>
+          <t>h_01KMZG877J1FGTK7QZB1DV7H2R</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-Active-Directory-and-Entra-ID-Integration-Guide/#h_01KMQ7VBW5CRXEP8KGFHBYG161</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-Active-Directory-and-Entra-ID-Integration-Guide/#h_01KMZG877J1FGTK7QZB1DV7H2R</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Tables</t>
+          <t>Policy</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -803,32 +803,98 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>h_01KMQ7WN0WEE2127MZ5RDTFBWD</t>
+          <t>h_01KMQ7TX7BWSQ5G56YKZ7PKWND</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-Active-Directory-and-Entra-ID-Integration-Guide/#h_01KMQ7WN0WEE2127MZ5RDTFBWD</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-Active-Directory-and-Entra-ID-Integration-Guide/#h_01KMQ7TX7BWSQ5G56YKZ7PKWND</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>Execution</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>h_01KMQ7V436R8NAB6DY1Q9CZ0K6</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-Active-Directory-and-Entra-ID-Integration-Guide/#h_01KMQ7V436R8NAB6DY1Q9CZ0K6</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Notification Center</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>h_01KMQ7VBW5CRXEP8KGFHBYG161</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-Active-Directory-and-Entra-ID-Integration-Guide/#h_01KMQ7VBW5CRXEP8KGFHBYG161</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Tables</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>h_01KMQ7WN0WEE2127MZ5RDTFBWD</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-Active-Directory-and-Entra-ID-Integration-Guide/#h_01KMQ7WN0WEE2127MZ5RDTFBWD</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
           <t>Schedule</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>H2</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
         <is>
           <t>h_01KMQ7VRVT1E4AD0BFY20V8496</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-Active-Directory-and-Entra-ID-Integration-Guide/#h_01KMQ7VRVT1E4AD0BFY20V8496</t>
         </is>

--- a/site/Dayforce-to-Active-Directory-and-Entra-ID-Integration-Guide/headings.xlsx
+++ b/site/Dayforce-to-Active-Directory-and-Entra-ID-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D22"/>
+  <dimension ref="A1:D23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -793,29 +793,29 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Policy</t>
+          <t>OneDrive Settings</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>h_01KMQ7TX7BWSQ5G56YKZ7PKWND</t>
+          <t>h_01KN1CVVCWWR4CJ9R85RM37GY4</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-Active-Directory-and-Entra-ID-Integration-Guide/#h_01KMQ7TX7BWSQ5G56YKZ7PKWND</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-Active-Directory-and-Entra-ID-Integration-Guide/#h_01KN1CVVCWWR4CJ9R85RM37GY4</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Execution</t>
+          <t>Policy</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -825,19 +825,19 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>h_01KMQ7V436R8NAB6DY1Q9CZ0K6</t>
+          <t>h_01KMQ7TX7BWSQ5G56YKZ7PKWND</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-Active-Directory-and-Entra-ID-Integration-Guide/#h_01KMQ7V436R8NAB6DY1Q9CZ0K6</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-Active-Directory-and-Entra-ID-Integration-Guide/#h_01KMQ7TX7BWSQ5G56YKZ7PKWND</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Notification Center</t>
+          <t>Execution</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -847,19 +847,19 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>h_01KMQ7VBW5CRXEP8KGFHBYG161</t>
+          <t>h_01KMQ7V436R8NAB6DY1Q9CZ0K6</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-Active-Directory-and-Entra-ID-Integration-Guide/#h_01KMQ7VBW5CRXEP8KGFHBYG161</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-Active-Directory-and-Entra-ID-Integration-Guide/#h_01KMQ7V436R8NAB6DY1Q9CZ0K6</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Tables</t>
+          <t>Notification Center</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -869,32 +869,54 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>h_01KMQ7WN0WEE2127MZ5RDTFBWD</t>
+          <t>h_01KMQ7VBW5CRXEP8KGFHBYG161</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-Active-Directory-and-Entra-ID-Integration-Guide/#h_01KMQ7WN0WEE2127MZ5RDTFBWD</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-Active-Directory-and-Entra-ID-Integration-Guide/#h_01KMQ7VBW5CRXEP8KGFHBYG161</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>Tables</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>h_01KMQ7WN0WEE2127MZ5RDTFBWD</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-Active-Directory-and-Entra-ID-Integration-Guide/#h_01KMQ7WN0WEE2127MZ5RDTFBWD</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
           <t>Schedule</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>H2</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
         <is>
           <t>h_01KMQ7VRVT1E4AD0BFY20V8496</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-Active-Directory-and-Entra-ID-Integration-Guide/#h_01KMQ7VRVT1E4AD0BFY20V8496</t>
         </is>

--- a/site/Dayforce-to-Active-Directory-and-Entra-ID-Integration-Guide/headings.xlsx
+++ b/site/Dayforce-to-Active-Directory-and-Entra-ID-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:D24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -803,41 +803,41 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>h_01KN1CVVCWWR4CJ9R85RM37GY4</t>
+          <t>h_01KN1K65GETWS7NCHS9W045TJX</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-Active-Directory-and-Entra-ID-Integration-Guide/#h_01KN1CVVCWWR4CJ9R85RM37GY4</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-Active-Directory-and-Entra-ID-Integration-Guide/#h_01KN1K65GETWS7NCHS9W045TJX</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Policy</t>
+          <t>Device Settings</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>h_01KMQ7TX7BWSQ5G56YKZ7PKWND</t>
+          <t>h_01KN1K65GF21Z5W8MVY1Z28RQY</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-Active-Directory-and-Entra-ID-Integration-Guide/#h_01KMQ7TX7BWSQ5G56YKZ7PKWND</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-Active-Directory-and-Entra-ID-Integration-Guide/#h_01KN1K65GF21Z5W8MVY1Z28RQY</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Execution</t>
+          <t>Policy</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -847,19 +847,19 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>h_01KMQ7V436R8NAB6DY1Q9CZ0K6</t>
+          <t>h_01KMQ7TX7BWSQ5G56YKZ7PKWND</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-Active-Directory-and-Entra-ID-Integration-Guide/#h_01KMQ7V436R8NAB6DY1Q9CZ0K6</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-Active-Directory-and-Entra-ID-Integration-Guide/#h_01KMQ7TX7BWSQ5G56YKZ7PKWND</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Notification Center</t>
+          <t>Execution</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -869,19 +869,19 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>h_01KMQ7VBW5CRXEP8KGFHBYG161</t>
+          <t>h_01KMQ7V436R8NAB6DY1Q9CZ0K6</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-Active-Directory-and-Entra-ID-Integration-Guide/#h_01KMQ7VBW5CRXEP8KGFHBYG161</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-Active-Directory-and-Entra-ID-Integration-Guide/#h_01KMQ7V436R8NAB6DY1Q9CZ0K6</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Tables</t>
+          <t>Notification Center</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -891,32 +891,54 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>h_01KMQ7WN0WEE2127MZ5RDTFBWD</t>
+          <t>h_01KMQ7VBW5CRXEP8KGFHBYG161</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-Active-Directory-and-Entra-ID-Integration-Guide/#h_01KMQ7WN0WEE2127MZ5RDTFBWD</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-Active-Directory-and-Entra-ID-Integration-Guide/#h_01KMQ7VBW5CRXEP8KGFHBYG161</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>Tables</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>h_01KMQ7WN0WEE2127MZ5RDTFBWD</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-Active-Directory-and-Entra-ID-Integration-Guide/#h_01KMQ7WN0WEE2127MZ5RDTFBWD</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
           <t>Schedule</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>H2</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
         <is>
           <t>h_01KMQ7VRVT1E4AD0BFY20V8496</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-Active-Directory-and-Entra-ID-Integration-Guide/#h_01KMQ7VRVT1E4AD0BFY20V8496</t>
         </is>

--- a/site/Dayforce-to-Active-Directory-and-Entra-ID-Integration-Guide/headings.xlsx
+++ b/site/Dayforce-to-Active-Directory-and-Entra-ID-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D24"/>
+  <dimension ref="A1:D26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -803,12 +803,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>h_01KN1K65GETWS7NCHS9W045TJX</t>
+          <t>h_01KN1PHQQ5H8A9AXCSFBY3PXV5</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-Active-Directory-and-Entra-ID-Integration-Guide/#h_01KN1K65GETWS7NCHS9W045TJX</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-Active-Directory-and-Entra-ID-Integration-Guide/#h_01KN1PHQQ5H8A9AXCSFBY3PXV5</t>
         </is>
       </c>
     </row>
@@ -825,63 +825,63 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>h_01KN1K65GF21Z5W8MVY1Z28RQY</t>
+          <t>h_01KN1PHQQ5BSRGQ01YB0AX1XCW</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-Active-Directory-and-Entra-ID-Integration-Guide/#h_01KN1K65GF21Z5W8MVY1Z28RQY</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-Active-Directory-and-Entra-ID-Integration-Guide/#h_01KN1PHQQ5BSRGQ01YB0AX1XCW</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Policy</t>
+          <t>Groups Settings</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>h_01KMQ7TX7BWSQ5G56YKZ7PKWND</t>
+          <t>h_01KN1PHQQ5QXK41PNX67R6F35P</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-Active-Directory-and-Entra-ID-Integration-Guide/#h_01KMQ7TX7BWSQ5G56YKZ7PKWND</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-Active-Directory-and-Entra-ID-Integration-Guide/#h_01KN1PHQQ5QXK41PNX67R6F35P</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Execution</t>
+          <t>WriteBack Settings</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>h_01KMQ7V436R8NAB6DY1Q9CZ0K6</t>
+          <t>h_01KN1PHQQ5711CX7ZN08ZXFV9W</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-Active-Directory-and-Entra-ID-Integration-Guide/#h_01KMQ7V436R8NAB6DY1Q9CZ0K6</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-Active-Directory-and-Entra-ID-Integration-Guide/#h_01KN1PHQQ5711CX7ZN08ZXFV9W</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Notification Center</t>
+          <t>Policy</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -891,19 +891,19 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>h_01KMQ7VBW5CRXEP8KGFHBYG161</t>
+          <t>h_01KMQ7TX7BWSQ5G56YKZ7PKWND</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-Active-Directory-and-Entra-ID-Integration-Guide/#h_01KMQ7VBW5CRXEP8KGFHBYG161</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-Active-Directory-and-Entra-ID-Integration-Guide/#h_01KMQ7TX7BWSQ5G56YKZ7PKWND</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Tables</t>
+          <t>Execution</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -913,32 +913,76 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>h_01KMQ7WN0WEE2127MZ5RDTFBWD</t>
+          <t>h_01KMQ7V436R8NAB6DY1Q9CZ0K6</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-Active-Directory-and-Entra-ID-Integration-Guide/#h_01KMQ7WN0WEE2127MZ5RDTFBWD</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-Active-Directory-and-Entra-ID-Integration-Guide/#h_01KMQ7V436R8NAB6DY1Q9CZ0K6</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
+          <t>Notification Center</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>h_01KMQ7VBW5CRXEP8KGFHBYG161</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-Active-Directory-and-Entra-ID-Integration-Guide/#h_01KMQ7VBW5CRXEP8KGFHBYG161</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Tables</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>h_01KMQ7WN0WEE2127MZ5RDTFBWD</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-Active-Directory-and-Entra-ID-Integration-Guide/#h_01KMQ7WN0WEE2127MZ5RDTFBWD</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
           <t>Schedule</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>H2</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
         <is>
           <t>h_01KMQ7VRVT1E4AD0BFY20V8496</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-Active-Directory-and-Entra-ID-Integration-Guide/#h_01KMQ7VRVT1E4AD0BFY20V8496</t>
         </is>

--- a/site/Dayforce-to-Active-Directory-and-Entra-ID-Integration-Guide/headings.xlsx
+++ b/site/Dayforce-to-Active-Directory-and-Entra-ID-Integration-Guide/headings.xlsx
@@ -781,12 +781,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>h_01KMZG877J1FGTK7QZB1DV7H2R</t>
+          <t>h_01KN1TBK83XCVZZF3RY26PJXS2</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-Active-Directory-and-Entra-ID-Integration-Guide/#h_01KMZG877J1FGTK7QZB1DV7H2R</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-Active-Directory-and-Entra-ID-Integration-Guide/#h_01KN1TBK83XCVZZF3RY26PJXS2</t>
         </is>
       </c>
     </row>
@@ -803,12 +803,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>h_01KN1PHQQ5H8A9AXCSFBY3PXV5</t>
+          <t>h_01KN1TBZY5Q4C9AN1ZHRDMXAHP</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-Active-Directory-and-Entra-ID-Integration-Guide/#h_01KN1PHQQ5H8A9AXCSFBY3PXV5</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-Active-Directory-and-Entra-ID-Integration-Guide/#h_01KN1TBZY5Q4C9AN1ZHRDMXAHP</t>
         </is>
       </c>
     </row>
@@ -825,12 +825,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>h_01KN1PHQQ5BSRGQ01YB0AX1XCW</t>
+          <t>h_01KN1TCB7YSSTH14250DTZDD4F</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-Active-Directory-and-Entra-ID-Integration-Guide/#h_01KN1PHQQ5BSRGQ01YB0AX1XCW</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-Active-Directory-and-Entra-ID-Integration-Guide/#h_01KN1TCB7YSSTH14250DTZDD4F</t>
         </is>
       </c>
     </row>
@@ -847,19 +847,19 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>h_01KN1PHQQ5QXK41PNX67R6F35P</t>
+          <t>h_01KN1TCKBWQRHN1ZKMW2Z7BQM6</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-Active-Directory-and-Entra-ID-Integration-Guide/#h_01KN1PHQQ5QXK41PNX67R6F35P</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-Active-Directory-and-Entra-ID-Integration-Guide/#h_01KN1TCKBWQRHN1ZKMW2Z7BQM6</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>WriteBack Settings</t>
+          <t>WriteBack Settings / Writeback Settings</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>h_01KN1PHQQ5711CX7ZN08ZXFV9W</t>
+          <t>h_01KMZG877J1FGTK7QZB1DV7H2R</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-Active-Directory-and-Entra-ID-Integration-Guide/#h_01KN1PHQQ5711CX7ZN08ZXFV9W</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-Active-Directory-and-Entra-ID-Integration-Guide/#h_01KMZG877J1FGTK7QZB1DV7H2R</t>
         </is>
       </c>
     </row>

--- a/site/Dayforce-to-Active-Directory-and-Entra-ID-Integration-Guide/headings.xlsx
+++ b/site/Dayforce-to-Active-Directory-and-Entra-ID-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D26"/>
+  <dimension ref="A1:D27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -988,6 +988,28 @@
         </is>
       </c>
     </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Provisioning Methods</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>h_01KN3VWFN63Z6QM0B9AGMBP9JY</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-Active-Directory-and-Entra-ID-Integration-Guide/#h_01KN3VWFN63Z6QM0B9AGMBP9JY</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/site/Dayforce-to-Active-Directory-and-Entra-ID-Integration-Guide/headings.xlsx
+++ b/site/Dayforce-to-Active-Directory-and-Entra-ID-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D27"/>
+  <dimension ref="A1:D28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -991,20 +991,42 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
+          <t>Appendix</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>h_01KN42W8X60FH5MKJE4RYF9CGN</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-Active-Directory-and-Entra-ID-Integration-Guide/#h_01KN42W8X60FH5MKJE4RYF9CGN</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
           <t>Provisioning Methods</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>H2</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
         <is>
           <t>h_01KN3VWFN63Z6QM0B9AGMBP9JY</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="D28" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-Active-Directory-and-Entra-ID-Integration-Guide/#h_01KN3VWFN63Z6QM0B9AGMBP9JY</t>
         </is>
